--- a/examples/inputs/template.xlsx
+++ b/examples/inputs/template.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="20">
   <si>
     <t>ticker</t>
   </si>
@@ -37,6 +37,27 @@
   </si>
   <si>
     <t>kurt</t>
+  </si>
+  <si>
+    <t>Equity DM</t>
+  </si>
+  <si>
+    <t>Equity EM</t>
+  </si>
+  <si>
+    <t>Real premia</t>
+  </si>
+  <si>
+    <t>Inflation</t>
+  </si>
+  <si>
+    <t>Credit</t>
+  </si>
+  <si>
+    <t>Commodity</t>
+  </si>
+  <si>
+    <t>Small cap</t>
   </si>
   <si>
     <t>factor</t>
@@ -445,12 +466,33 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -468,13 +510,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -489,13 +531,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -510,7 +552,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -537,13 +579,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
